--- a/отчеты для СН/ПОКОМ ЗПФ/Бердянск ПОКОМ ЗПФ.xlsx
+++ b/отчеты для СН/ПОКОМ ЗПФ/Бердянск ПОКОМ ЗПФ.xlsx
@@ -1,29 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\отчеты для СН\ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AF389E-FD2E-45FC-AE1F-9917562A95C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C9654D-7C5E-42B9-8B0B-804732DF8E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЗПФ" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -182,12 +174,12 @@
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -631,14 +623,14 @@
         <v>2.1</v>
       </c>
       <c r="E3" s="4">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="F3" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G14" si="0">D3+E3-F3</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H3" s="4">
         <f>4*J3</f>
@@ -660,13 +652,13 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" ref="D4:D14" si="1">G3</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H4" s="4">
         <f>H3</f>
@@ -685,13 +677,13 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H14" si="2">H4</f>
@@ -710,7 +702,7 @@
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4">
@@ -718,7 +710,7 @@
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="2"/>
@@ -737,17 +729,17 @@
       </c>
       <c r="D7" s="3">
         <f t="shared" si="1"/>
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="E7" s="4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F7" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>13.6</v>
+        <v>13.000000000000002</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="2"/>
@@ -766,7 +758,7 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="1"/>
-        <v>13.6</v>
+        <v>13.000000000000002</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4">
@@ -774,7 +766,7 @@
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>11.900000000000002</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="2"/>
@@ -793,7 +785,7 @@
       </c>
       <c r="D9" s="3">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>11.900000000000002</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4">
@@ -801,7 +793,7 @@
       </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
-        <v>11.4</v>
+        <v>10.800000000000002</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="2"/>
@@ -820,7 +812,7 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" si="1"/>
-        <v>11.4</v>
+        <v>10.800000000000002</v>
       </c>
       <c r="E10" s="4">
         <v>5.3</v>
@@ -830,7 +822,7 @@
       </c>
       <c r="G10" s="4">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" si="2"/>
@@ -849,13 +841,13 @@
       </c>
       <c r="D11" s="3">
         <f t="shared" si="1"/>
-        <v>15.6</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="H11" s="4">
         <f t="shared" si="2"/>
@@ -874,13 +866,13 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" si="1"/>
-        <v>15.6</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="2"/>
@@ -899,7 +891,7 @@
       </c>
       <c r="D13" s="3">
         <f t="shared" si="1"/>
-        <v>15.6</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4">
@@ -907,7 +899,7 @@
       </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
-        <v>14.5</v>
+        <v>13.900000000000002</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="2"/>
@@ -926,7 +918,7 @@
       </c>
       <c r="D14" s="3">
         <f t="shared" si="1"/>
-        <v>14.5</v>
+        <v>13.900000000000002</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4">
@@ -934,7 +926,7 @@
       </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
-        <v>13.4</v>
+        <v>12.800000000000002</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="2"/>
@@ -950,7 +942,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="4">
         <f>SUM(E3:E14)</f>
-        <v>20.100000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="F15" s="4">
         <f>SUM(F3:F14)</f>
